--- a/samagam result data/middle_marks_Written_Work_Maths.xlsx
+++ b/samagam result data/middle_marks_Written_Work_Maths.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/samagam result data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_747EBE3DD42011668355306ED7B687695CCC2BEE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A7E351E-D7A5-4729-B9F1-13CEC357B56E}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Marks" sheetId="1" r:id="rId4"/>
+    <sheet name="Marks" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Roll No</t>
   </si>
@@ -152,23 +157,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -195,14 +192,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -492,14 +497,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -527,7 +533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -541,7 +547,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -555,7 +561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -569,7 +575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -583,7 +589,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -597,7 +603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -611,7 +617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -625,7 +631,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -639,7 +645,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -653,7 +659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -667,7 +673,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -681,7 +687,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -695,7 +701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -709,7 +715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -723,7 +729,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -737,7 +743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -751,7 +757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -765,7 +771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -779,7 +785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -793,7 +799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -807,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -821,7 +827,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -835,7 +841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -849,7 +855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -863,7 +869,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -877,7 +883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -891,7 +897,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -905,7 +911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -919,7 +925,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -933,7 +939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -947,7 +953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -961,7 +967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -975,7 +981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -989,7 +995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1003,7 +1009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1017,7 +1023,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1031,7 +1037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1045,7 +1051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1059,7 +1065,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1074,8 +1080,6 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>